--- a/projects/fleet-maintenance-work-order-tracker/Fleet_Maintenance_Work_Order_Tracker.xlsx
+++ b/projects/fleet-maintenance-work-order-tracker/Fleet_Maintenance_Work_Order_Tracker.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{09C715F0-95F6-4F63-8DD4-AED1B90A30C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5945A816-0466-44B0-88FF-D658AECC9287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
   </definedNames>
   <calcPr calcId="191029" forceFullCalc="1"/>
   <pivotCaches>
-    <pivotCache cacheId="14" r:id="rId9"/>
+    <pivotCache cacheId="7" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="139">
   <si>
     <t>Priority</t>
   </si>
@@ -463,6 +463,9 @@
   </si>
   <si>
     <t>Synthetic QA approval definition edge case</t>
+  </si>
+  <si>
+    <t>Approvals Requiring Action</t>
   </si>
 </sst>
 </file>
@@ -607,6 +610,47 @@
   </cellStyles>
   <dxfs count="24">
     <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE5CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
@@ -659,47 +703,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -937,7 +940,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Author" refreshedDate="46318.994293402779" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="13" xr:uid="{12AAC19A-9298-4236-97AE-615911F82E28}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Author" refreshedDate="46320.053511111109" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="13" xr:uid="{12AAC19A-9298-4236-97AE-615911F82E28}">
   <cacheSource type="worksheet">
     <worksheetSource name="WorkOrdersTable"/>
   </cacheSource>
@@ -1017,7 +1020,7 @@
       <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-10-04T00:00:00" maxDate="2026-10-06T00:00:00"/>
     </cacheField>
     <cacheField name="Ageing (Days)" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="28"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2" maxValue="30"/>
     </cacheField>
     <cacheField name="Overdue?" numFmtId="0">
       <sharedItems/>
@@ -1056,7 +1059,7 @@
     <s v="Not Required"/>
     <d v="2026-10-03T00:00:00"/>
     <m/>
-    <n v="22"/>
+    <n v="24"/>
     <s v="Yes"/>
     <s v="Vehicle held for inspection"/>
     <s v="No Approval Action"/>
@@ -1078,7 +1081,7 @@
     <s v="Pending"/>
     <d v="2026-10-02T00:00:00"/>
     <m/>
-    <n v="25"/>
+    <n v="27"/>
     <s v="Yes"/>
     <s v="Vendor estimate received"/>
     <s v="Approval Follow-up"/>
@@ -1100,7 +1103,7 @@
     <s v="Not Required"/>
     <d v="2026-10-08T00:00:00"/>
     <m/>
-    <n v="21"/>
+    <n v="23"/>
     <s v="Yes"/>
     <s v="Replacement tires available"/>
     <s v="No Approval Action"/>
@@ -1144,7 +1147,7 @@
     <s v="Not Required"/>
     <d v="2026-10-12T00:00:00"/>
     <m/>
-    <n v="20"/>
+    <n v="22"/>
     <s v="Yes"/>
     <s v="Scheduled service"/>
     <s v="No Approval Action"/>
@@ -1166,7 +1169,7 @@
     <s v="Approved"/>
     <d v="2026-10-01T00:00:00"/>
     <m/>
-    <n v="28"/>
+    <n v="30"/>
     <s v="Yes"/>
     <s v="Parts ordered"/>
     <s v="No Approval Action"/>
@@ -1188,7 +1191,7 @@
     <s v="Not Required"/>
     <d v="2026-10-15T00:00:00"/>
     <m/>
-    <n v="18"/>
+    <n v="20"/>
     <s v="Yes"/>
     <s v="Awaiting inspection"/>
     <s v="No Approval Action"/>
@@ -1210,7 +1213,7 @@
     <s v="Approved"/>
     <d v="2026-10-04T00:00:00"/>
     <m/>
-    <n v="26"/>
+    <n v="28"/>
     <s v="Yes"/>
     <s v="Appointment booked"/>
     <s v="No Approval Action"/>
@@ -1232,7 +1235,7 @@
     <s v="Not Required"/>
     <d v="2026-10-07T00:00:00"/>
     <m/>
-    <n v="17"/>
+    <n v="19"/>
     <s v="Yes"/>
     <s v="Diagnostics underway"/>
     <s v="No Approval Action"/>
@@ -1276,7 +1279,7 @@
     <s v="Pending"/>
     <d v="2026-11-09T00:00:00"/>
     <m/>
-    <n v="0"/>
+    <n v="2"/>
     <s v="No"/>
     <s v="Synthetic QA edge case"/>
     <s v="Approval Follow-up"/>
@@ -1298,7 +1301,7 @@
     <s v="Not Required"/>
     <d v="2026-11-09T00:00:00"/>
     <m/>
-    <n v="0"/>
+    <n v="2"/>
     <s v="No"/>
     <s v="Synthetic QA cost expansion"/>
     <s v="No Approval Action"/>
@@ -1320,7 +1323,7 @@
     <s v="Pending"/>
     <d v="2026-11-09T00:00:00"/>
     <m/>
-    <n v="0"/>
+    <n v="2"/>
     <s v="No"/>
     <s v="Synthetic QA approval definition edge case"/>
     <s v="No Approval Action"/>
@@ -1329,7 +1332,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3A4FDF88-4442-44B2-8403-64B8EC07FE6C}" name="PivotTable1" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3A4FDF88-4442-44B2-8403-64B8EC07FE6C}" name="PivotTable1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="20">
     <pivotField dataField="1" showAll="0"/>
@@ -1408,7 +1411,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0589CE3D-19BC-4FCE-8CDC-E6C15A767060}" name="PivotTable2" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0589CE3D-19BC-4FCE-8CDC-E6C15A767060}" name="PivotTable2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:E11" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="20">
     <pivotField dataField="1" showAll="0"/>
@@ -1508,7 +1511,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C706A4B5-2902-458A-B3CE-98EFA3475A6D}" name="PivotTable3" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C706A4B5-2902-458A-B3CE-98EFA3475A6D}" name="PivotTable3" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="20">
     <pivotField showAll="0"/>
@@ -1623,26 +1626,26 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{09002EC3-3A1A-4C11-B001-F848F34A9A95}" name="WorkOrdersTable_1" displayName="WorkOrdersTable_1" ref="A1:T14" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:T14" xr:uid="{09002EC3-3A1A-4C11-B001-F848F34A9A95}"/>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{08A20C5F-D549-4DD2-B882-294D1B3E7517}" uniqueName="1" name="Work Order ID" queryTableFieldId="1" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{C3C76C9A-B8ED-4551-8C25-533C9DA5DDA4}" uniqueName="2" name="Vehicle / Equipment ID" queryTableFieldId="2" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{CD715C2E-FEBA-4420-91CC-557EA02F407F}" uniqueName="3" name="Department" queryTableFieldId="3" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{B56AF665-823A-4F7B-B67A-B279AF19C1F9}" uniqueName="4" name="Issue Category" queryTableFieldId="4" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{61D0327D-8F0E-4B68-8B75-9431C02DC910}" uniqueName="5" name="Issue Description" queryTableFieldId="5" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{D298D72F-3CC0-4733-B9FF-20F93A8F903E}" uniqueName="6" name="Priority" queryTableFieldId="6" dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{590D5F60-9D07-4947-A49B-9E86136EE866}" uniqueName="7" name="Reported Date" queryTableFieldId="7" dataDxfId="11"/>
-    <tableColumn id="8" xr3:uid="{599C74A2-ECB3-4026-98F4-300FF4EFFB1F}" uniqueName="8" name="Assigned To" queryTableFieldId="8" dataDxfId="10"/>
-    <tableColumn id="9" xr3:uid="{E70E21E5-ED6A-477D-99D2-5A4D2F299BFF}" uniqueName="9" name="Assignee Type" queryTableFieldId="9" dataDxfId="9"/>
-    <tableColumn id="10" xr3:uid="{85D887FA-4E59-4685-9B8A-D18B6D70CEA8}" uniqueName="10" name="Assignment Type" queryTableFieldId="10" dataDxfId="8"/>
-    <tableColumn id="11" xr3:uid="{471D2E11-B56A-4E6E-B7B4-D60EC960FEA3}" uniqueName="11" name="Status" queryTableFieldId="11" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{08A20C5F-D549-4DD2-B882-294D1B3E7517}" uniqueName="1" name="Work Order ID" queryTableFieldId="1" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{C3C76C9A-B8ED-4551-8C25-533C9DA5DDA4}" uniqueName="2" name="Vehicle / Equipment ID" queryTableFieldId="2" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{CD715C2E-FEBA-4420-91CC-557EA02F407F}" uniqueName="3" name="Department" queryTableFieldId="3" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{B56AF665-823A-4F7B-B67A-B279AF19C1F9}" uniqueName="4" name="Issue Category" queryTableFieldId="4" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{61D0327D-8F0E-4B68-8B75-9431C02DC910}" uniqueName="5" name="Issue Description" queryTableFieldId="5" dataDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{D298D72F-3CC0-4733-B9FF-20F93A8F903E}" uniqueName="6" name="Priority" queryTableFieldId="6" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{590D5F60-9D07-4947-A49B-9E86136EE866}" uniqueName="7" name="Reported Date" queryTableFieldId="7" dataDxfId="17"/>
+    <tableColumn id="8" xr3:uid="{599C74A2-ECB3-4026-98F4-300FF4EFFB1F}" uniqueName="8" name="Assigned To" queryTableFieldId="8" dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{E70E21E5-ED6A-477D-99D2-5A4D2F299BFF}" uniqueName="9" name="Assignee Type" queryTableFieldId="9" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{85D887FA-4E59-4685-9B8A-D18B6D70CEA8}" uniqueName="10" name="Assignment Type" queryTableFieldId="10" dataDxfId="14"/>
+    <tableColumn id="11" xr3:uid="{471D2E11-B56A-4E6E-B7B4-D60EC960FEA3}" uniqueName="11" name="Status" queryTableFieldId="11" dataDxfId="13"/>
     <tableColumn id="12" xr3:uid="{29C5F8E3-F6E1-4896-8F22-0720E281F076}" uniqueName="12" name="Estimated Cost" queryTableFieldId="12"/>
-    <tableColumn id="13" xr3:uid="{5C097BC8-EE87-4C13-AAE8-01672938486E}" uniqueName="13" name="Approval Required" queryTableFieldId="13" dataDxfId="6"/>
-    <tableColumn id="14" xr3:uid="{09078007-210D-4EE3-BFDA-3E423ADBFD4E}" uniqueName="14" name="Approval Status" queryTableFieldId="14" dataDxfId="5"/>
-    <tableColumn id="15" xr3:uid="{AB7D9A2E-BBAF-4005-BF3F-38364708BD06}" uniqueName="15" name="Due Date" queryTableFieldId="15" dataDxfId="4"/>
-    <tableColumn id="16" xr3:uid="{3FE5958C-68B4-4752-822F-5DD046111A4D}" uniqueName="16" name="Completion Date" queryTableFieldId="16" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{5C097BC8-EE87-4C13-AAE8-01672938486E}" uniqueName="13" name="Approval Required" queryTableFieldId="13" dataDxfId="12"/>
+    <tableColumn id="14" xr3:uid="{09078007-210D-4EE3-BFDA-3E423ADBFD4E}" uniqueName="14" name="Approval Status" queryTableFieldId="14" dataDxfId="11"/>
+    <tableColumn id="15" xr3:uid="{AB7D9A2E-BBAF-4005-BF3F-38364708BD06}" uniqueName="15" name="Due Date" queryTableFieldId="15" dataDxfId="10"/>
+    <tableColumn id="16" xr3:uid="{3FE5958C-68B4-4752-822F-5DD046111A4D}" uniqueName="16" name="Completion Date" queryTableFieldId="16" dataDxfId="9"/>
     <tableColumn id="17" xr3:uid="{BED07573-22BB-4E58-9358-D3CC2A48E178}" uniqueName="17" name="Ageing (Days)" queryTableFieldId="17"/>
-    <tableColumn id="18" xr3:uid="{C6A879F2-8F48-45E5-9587-C3F8AD882CE2}" uniqueName="18" name="Overdue?" queryTableFieldId="18" dataDxfId="2"/>
-    <tableColumn id="19" xr3:uid="{6049AE64-1BEE-424A-B12D-3DD97C4A502A}" uniqueName="19" name="Notes" queryTableFieldId="19" dataDxfId="1"/>
-    <tableColumn id="20" xr3:uid="{906D965D-195F-47F4-992D-D2D60A15F26B}" uniqueName="20" name="Action Required" queryTableFieldId="20" dataDxfId="0"/>
+    <tableColumn id="18" xr3:uid="{C6A879F2-8F48-45E5-9587-C3F8AD882CE2}" uniqueName="18" name="Overdue?" queryTableFieldId="18" dataDxfId="8"/>
+    <tableColumn id="19" xr3:uid="{6049AE64-1BEE-424A-B12D-3DD97C4A502A}" uniqueName="19" name="Notes" queryTableFieldId="19" dataDxfId="7"/>
+    <tableColumn id="20" xr3:uid="{906D965D-195F-47F4-992D-D2D60A15F26B}" uniqueName="20" name="Action Required" queryTableFieldId="20" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1659,7 +1662,7 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Priority"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Reported Date"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Assigned To"/>
-    <tableColumn id="20" xr3:uid="{436BC114-7025-48C2-AEB2-3996CEAB0DFC}" name="Assignee Type" dataDxfId="23">
+    <tableColumn id="20" xr3:uid="{436BC114-7025-48C2-AEB2-3996CEAB0DFC}" name="Assignee Type" dataDxfId="5">
       <calculatedColumnFormula>_xlfn.XLOOKUP(H2,Assignee_Lookup!$A$2:$A$7,Assignee_Lookup!$B$2:$B$7,"Not Found")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Assignment Type"/>
@@ -1672,7 +1675,7 @@
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Ageing (Days)"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Overdue?"/>
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Notes"/>
-    <tableColumn id="19" xr3:uid="{772450BC-10A6-4B19-9D6E-8009E2775CC1}" name="Action Required" dataDxfId="22">
+    <tableColumn id="19" xr3:uid="{772450BC-10A6-4B19-9D6E-8009E2775CC1}" name="Action Required" dataDxfId="4">
       <calculatedColumnFormula>IF(AND(M2="Yes",N2="Pending"),"Approval Follow-up","No Approval Action")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2589,46 +2592,46 @@
       </c>
     </row>
     <row r="2" spans="1:20">
-      <c r="A2" s="21" t="s">
+      <c r="A2" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" t="s">
         <v>52</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" t="s">
         <v>6</v>
       </c>
       <c r="G2" s="18">
         <v>46296</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="I2" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="J2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="K2" t="s">
         <v>19</v>
       </c>
       <c r="L2">
         <v>850</v>
       </c>
-      <c r="M2" s="21" t="s">
+      <c r="M2" t="s">
         <v>53</v>
       </c>
-      <c r="N2" s="21" t="s">
+      <c r="N2" t="s">
         <v>54</v>
       </c>
       <c r="O2" s="18">
@@ -2638,57 +2641,57 @@
       <c r="Q2">
         <v>22</v>
       </c>
-      <c r="R2" s="21" t="s">
+      <c r="R2" t="s">
         <v>59</v>
       </c>
-      <c r="S2" s="21" t="s">
+      <c r="S2" t="s">
         <v>55</v>
       </c>
-      <c r="T2" s="21" t="s">
+      <c r="T2" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:20">
-      <c r="A3" s="21" t="s">
+      <c r="A3" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" t="s">
         <v>58</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" t="s">
         <v>6</v>
       </c>
       <c r="G3" s="18">
         <v>46293</v>
       </c>
-      <c r="H3" s="21" t="s">
+      <c r="H3" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="21" t="s">
+      <c r="I3" t="s">
         <v>112</v>
       </c>
-      <c r="J3" s="21" t="s">
+      <c r="J3" t="s">
         <v>16</v>
       </c>
-      <c r="K3" s="21" t="s">
+      <c r="K3" t="s">
         <v>23</v>
       </c>
       <c r="L3">
         <v>4200</v>
       </c>
-      <c r="M3" s="21" t="s">
+      <c r="M3" t="s">
         <v>59</v>
       </c>
-      <c r="N3" s="21" t="s">
+      <c r="N3" t="s">
         <v>60</v>
       </c>
       <c r="O3" s="18">
@@ -2698,57 +2701,57 @@
       <c r="Q3">
         <v>25</v>
       </c>
-      <c r="R3" s="21" t="s">
+      <c r="R3" t="s">
         <v>59</v>
       </c>
-      <c r="S3" s="21" t="s">
+      <c r="S3" t="s">
         <v>61</v>
       </c>
-      <c r="T3" s="21" t="s">
+      <c r="T3" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:20">
-      <c r="A4" s="21" t="s">
+      <c r="A4" t="s">
         <v>62</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" t="s">
         <v>12</v>
       </c>
       <c r="G4" s="18">
         <v>46297</v>
       </c>
-      <c r="H4" s="21" t="s">
+      <c r="H4" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="21" t="s">
+      <c r="I4" t="s">
         <v>110</v>
       </c>
-      <c r="J4" s="21" t="s">
+      <c r="J4" t="s">
         <v>10</v>
       </c>
-      <c r="K4" s="21" t="s">
+      <c r="K4" t="s">
         <v>13</v>
       </c>
       <c r="L4">
         <v>620</v>
       </c>
-      <c r="M4" s="21" t="s">
+      <c r="M4" t="s">
         <v>53</v>
       </c>
-      <c r="N4" s="21" t="s">
+      <c r="N4" t="s">
         <v>54</v>
       </c>
       <c r="O4" s="18">
@@ -2758,57 +2761,57 @@
       <c r="Q4">
         <v>21</v>
       </c>
-      <c r="R4" s="21" t="s">
+      <c r="R4" t="s">
         <v>59</v>
       </c>
-      <c r="S4" s="21" t="s">
+      <c r="S4" t="s">
         <v>65</v>
       </c>
-      <c r="T4" s="21" t="s">
+      <c r="T4" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:20">
-      <c r="A5" s="21" t="s">
+      <c r="A5" t="s">
         <v>66</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" t="s">
         <v>68</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" t="s">
         <v>12</v>
       </c>
       <c r="G5" s="18">
         <v>46295</v>
       </c>
-      <c r="H5" s="21" t="s">
+      <c r="H5" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="21" t="s">
+      <c r="I5" t="s">
         <v>112</v>
       </c>
-      <c r="J5" s="21" t="s">
+      <c r="J5" t="s">
         <v>16</v>
       </c>
-      <c r="K5" s="21" t="s">
+      <c r="K5" t="s">
         <v>27</v>
       </c>
       <c r="L5">
         <v>540</v>
       </c>
-      <c r="M5" s="21" t="s">
+      <c r="M5" t="s">
         <v>53</v>
       </c>
-      <c r="N5" s="21" t="s">
+      <c r="N5" t="s">
         <v>54</v>
       </c>
       <c r="O5" s="18">
@@ -2820,57 +2823,57 @@
       <c r="Q5">
         <v>4</v>
       </c>
-      <c r="R5" s="21" t="s">
+      <c r="R5" t="s">
         <v>53</v>
       </c>
-      <c r="S5" s="21" t="s">
+      <c r="S5" t="s">
         <v>69</v>
       </c>
-      <c r="T5" s="21" t="s">
+      <c r="T5" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:20">
-      <c r="A6" s="21" t="s">
+      <c r="A6" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" t="s">
         <v>71</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" t="s">
         <v>72</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="F6" t="s">
         <v>18</v>
       </c>
       <c r="G6" s="18">
         <v>46298</v>
       </c>
-      <c r="H6" s="21" t="s">
+      <c r="H6" t="s">
         <v>30</v>
       </c>
-      <c r="I6" s="21" t="s">
+      <c r="I6" t="s">
         <v>110</v>
       </c>
-      <c r="J6" s="21" t="s">
+      <c r="J6" t="s">
         <v>10</v>
       </c>
-      <c r="K6" s="21" t="s">
+      <c r="K6" t="s">
         <v>7</v>
       </c>
       <c r="L6">
         <v>300</v>
       </c>
-      <c r="M6" s="21" t="s">
+      <c r="M6" t="s">
         <v>53</v>
       </c>
-      <c r="N6" s="21" t="s">
+      <c r="N6" t="s">
         <v>54</v>
       </c>
       <c r="O6" s="18">
@@ -2880,57 +2883,57 @@
       <c r="Q6">
         <v>20</v>
       </c>
-      <c r="R6" s="21" t="s">
+      <c r="R6" t="s">
         <v>59</v>
       </c>
-      <c r="S6" s="21" t="s">
+      <c r="S6" t="s">
         <v>73</v>
       </c>
-      <c r="T6" s="21" t="s">
+      <c r="T6" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:20">
-      <c r="A7" s="21" t="s">
+      <c r="A7" t="s">
         <v>74</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="21" t="s">
+      <c r="E7" t="s">
         <v>76</v>
       </c>
-      <c r="F7" s="21" t="s">
+      <c r="F7" t="s">
         <v>12</v>
       </c>
       <c r="G7" s="18">
         <v>46290</v>
       </c>
-      <c r="H7" s="21" t="s">
+      <c r="H7" t="s">
         <v>34</v>
       </c>
-      <c r="I7" s="21" t="s">
+      <c r="I7" t="s">
         <v>112</v>
       </c>
-      <c r="J7" s="21" t="s">
+      <c r="J7" t="s">
         <v>16</v>
       </c>
-      <c r="K7" s="21" t="s">
+      <c r="K7" t="s">
         <v>19</v>
       </c>
       <c r="L7">
         <v>1450</v>
       </c>
-      <c r="M7" s="21" t="s">
+      <c r="M7" t="s">
         <v>59</v>
       </c>
-      <c r="N7" s="21" t="s">
+      <c r="N7" t="s">
         <v>77</v>
       </c>
       <c r="O7" s="18">
@@ -2940,57 +2943,57 @@
       <c r="Q7">
         <v>28</v>
       </c>
-      <c r="R7" s="21" t="s">
+      <c r="R7" t="s">
         <v>59</v>
       </c>
-      <c r="S7" s="21" t="s">
+      <c r="S7" t="s">
         <v>78</v>
       </c>
-      <c r="T7" s="21" t="s">
+      <c r="T7" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:20">
-      <c r="A8" s="21" t="s">
+      <c r="A8" t="s">
         <v>79</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" t="s">
         <v>80</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" t="s">
         <v>81</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F8" t="s">
         <v>18</v>
       </c>
       <c r="G8" s="18">
         <v>46300</v>
       </c>
-      <c r="H8" s="21" t="s">
+      <c r="H8" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="21" t="s">
+      <c r="I8" t="s">
         <v>110</v>
       </c>
-      <c r="J8" s="21" t="s">
+      <c r="J8" t="s">
         <v>10</v>
       </c>
-      <c r="K8" s="21" t="s">
+      <c r="K8" t="s">
         <v>7</v>
       </c>
       <c r="L8">
         <v>950</v>
       </c>
-      <c r="M8" s="21" t="s">
+      <c r="M8" t="s">
         <v>53</v>
       </c>
-      <c r="N8" s="21" t="s">
+      <c r="N8" t="s">
         <v>54</v>
       </c>
       <c r="O8" s="18">
@@ -3000,57 +3003,57 @@
       <c r="Q8">
         <v>18</v>
       </c>
-      <c r="R8" s="21" t="s">
+      <c r="R8" t="s">
         <v>59</v>
       </c>
-      <c r="S8" s="21" t="s">
+      <c r="S8" t="s">
         <v>82</v>
       </c>
-      <c r="T8" s="21" t="s">
+      <c r="T8" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:20">
-      <c r="A9" s="21" t="s">
+      <c r="A9" t="s">
         <v>83</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="E9" t="s">
         <v>85</v>
       </c>
-      <c r="F9" s="21" t="s">
+      <c r="F9" t="s">
         <v>12</v>
       </c>
       <c r="G9" s="18">
         <v>46292</v>
       </c>
-      <c r="H9" s="21" t="s">
+      <c r="H9" t="s">
         <v>17</v>
       </c>
-      <c r="I9" s="21" t="s">
+      <c r="I9" t="s">
         <v>112</v>
       </c>
-      <c r="J9" s="21" t="s">
+      <c r="J9" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="21" t="s">
+      <c r="K9" t="s">
         <v>13</v>
       </c>
       <c r="L9">
         <v>1800</v>
       </c>
-      <c r="M9" s="21" t="s">
+      <c r="M9" t="s">
         <v>59</v>
       </c>
-      <c r="N9" s="21" t="s">
+      <c r="N9" t="s">
         <v>77</v>
       </c>
       <c r="O9" s="18">
@@ -3060,57 +3063,57 @@
       <c r="Q9">
         <v>26</v>
       </c>
-      <c r="R9" s="21" t="s">
+      <c r="R9" t="s">
         <v>59</v>
       </c>
-      <c r="S9" s="21" t="s">
+      <c r="S9" t="s">
         <v>86</v>
       </c>
-      <c r="T9" s="21" t="s">
+      <c r="T9" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:20">
-      <c r="A10" s="21" t="s">
+      <c r="A10" t="s">
         <v>87</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" t="s">
         <v>88</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="21" t="s">
+      <c r="E10" t="s">
         <v>89</v>
       </c>
-      <c r="F10" s="21" t="s">
+      <c r="F10" t="s">
         <v>6</v>
       </c>
       <c r="G10" s="18">
         <v>46301</v>
       </c>
-      <c r="H10" s="21" t="s">
+      <c r="H10" t="s">
         <v>22</v>
       </c>
-      <c r="I10" s="21" t="s">
+      <c r="I10" t="s">
         <v>110</v>
       </c>
-      <c r="J10" s="21" t="s">
+      <c r="J10" t="s">
         <v>10</v>
       </c>
-      <c r="K10" s="21" t="s">
+      <c r="K10" t="s">
         <v>19</v>
       </c>
       <c r="L10">
         <v>1100</v>
       </c>
-      <c r="M10" s="21" t="s">
+      <c r="M10" t="s">
         <v>53</v>
       </c>
-      <c r="N10" s="21" t="s">
+      <c r="N10" t="s">
         <v>54</v>
       </c>
       <c r="O10" s="18">
@@ -3120,57 +3123,57 @@
       <c r="Q10">
         <v>17</v>
       </c>
-      <c r="R10" s="21" t="s">
+      <c r="R10" t="s">
         <v>59</v>
       </c>
-      <c r="S10" s="21" t="s">
+      <c r="S10" t="s">
         <v>90</v>
       </c>
-      <c r="T10" s="21" t="s">
+      <c r="T10" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:20">
-      <c r="A11" s="21" t="s">
+      <c r="A11" t="s">
         <v>91</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" t="s">
         <v>92</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="21" t="s">
+      <c r="D11" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="E11" t="s">
         <v>93</v>
       </c>
-      <c r="F11" s="21" t="s">
+      <c r="F11" t="s">
         <v>12</v>
       </c>
       <c r="G11" s="18">
         <v>46296</v>
       </c>
-      <c r="H11" s="21" t="s">
+      <c r="H11" t="s">
         <v>26</v>
       </c>
-      <c r="I11" s="21" t="s">
+      <c r="I11" t="s">
         <v>112</v>
       </c>
-      <c r="J11" s="21" t="s">
+      <c r="J11" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="21" t="s">
+      <c r="K11" t="s">
         <v>31</v>
       </c>
       <c r="L11">
         <v>900</v>
       </c>
-      <c r="M11" s="21" t="s">
+      <c r="M11" t="s">
         <v>53</v>
       </c>
-      <c r="N11" s="21" t="s">
+      <c r="N11" t="s">
         <v>54</v>
       </c>
       <c r="O11" s="18">
@@ -3182,57 +3185,57 @@
       <c r="Q11">
         <v>4</v>
       </c>
-      <c r="R11" s="21" t="s">
+      <c r="R11" t="s">
         <v>53</v>
       </c>
-      <c r="S11" s="21" t="s">
+      <c r="S11" t="s">
         <v>94</v>
       </c>
-      <c r="T11" s="21" t="s">
+      <c r="T11" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:20">
-      <c r="A12" s="21" t="s">
+      <c r="A12" t="s">
         <v>126</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" t="s">
         <v>127</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="C12" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="21" t="s">
+      <c r="D12" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="21" t="s">
+      <c r="E12" t="s">
         <v>128</v>
       </c>
-      <c r="F12" s="21" t="s">
+      <c r="F12" t="s">
         <v>12</v>
       </c>
       <c r="G12" s="18">
         <v>46318</v>
       </c>
-      <c r="H12" s="21" t="s">
+      <c r="H12" t="s">
         <v>11</v>
       </c>
-      <c r="I12" s="21" t="s">
+      <c r="I12" t="s">
         <v>110</v>
       </c>
-      <c r="J12" s="21" t="s">
+      <c r="J12" t="s">
         <v>10</v>
       </c>
-      <c r="K12" s="21" t="s">
+      <c r="K12" t="s">
         <v>19</v>
       </c>
       <c r="L12">
         <v>350</v>
       </c>
-      <c r="M12" s="21" t="s">
+      <c r="M12" t="s">
         <v>59</v>
       </c>
-      <c r="N12" s="21" t="s">
+      <c r="N12" t="s">
         <v>60</v>
       </c>
       <c r="O12" s="18">
@@ -3242,57 +3245,57 @@
       <c r="Q12">
         <v>0</v>
       </c>
-      <c r="R12" s="21" t="s">
+      <c r="R12" t="s">
         <v>53</v>
       </c>
-      <c r="S12" s="21" t="s">
+      <c r="S12" t="s">
         <v>129</v>
       </c>
-      <c r="T12" s="21" t="s">
+      <c r="T12" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:20">
-      <c r="A13" s="21" t="s">
+      <c r="A13" t="s">
         <v>130</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B13" t="s">
         <v>131</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" t="s">
         <v>15</v>
       </c>
-      <c r="D13" s="21" t="s">
+      <c r="D13" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="21" t="s">
+      <c r="E13" t="s">
         <v>132</v>
       </c>
-      <c r="F13" s="21" t="s">
+      <c r="F13" t="s">
         <v>18</v>
       </c>
       <c r="G13" s="18">
         <v>46318</v>
       </c>
-      <c r="H13" s="21" t="s">
+      <c r="H13" t="s">
         <v>11</v>
       </c>
-      <c r="I13" s="21" t="s">
+      <c r="I13" t="s">
         <v>110</v>
       </c>
-      <c r="J13" s="21" t="s">
+      <c r="J13" t="s">
         <v>10</v>
       </c>
-      <c r="K13" s="21" t="s">
+      <c r="K13" t="s">
         <v>7</v>
       </c>
       <c r="L13">
         <v>500</v>
       </c>
-      <c r="M13" s="21" t="s">
+      <c r="M13" t="s">
         <v>53</v>
       </c>
-      <c r="N13" s="21" t="s">
+      <c r="N13" t="s">
         <v>54</v>
       </c>
       <c r="O13" s="18">
@@ -3302,57 +3305,57 @@
       <c r="Q13">
         <v>0</v>
       </c>
-      <c r="R13" s="21" t="s">
+      <c r="R13" t="s">
         <v>53</v>
       </c>
-      <c r="S13" s="21" t="s">
+      <c r="S13" t="s">
         <v>133</v>
       </c>
-      <c r="T13" s="21" t="s">
+      <c r="T13" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:20">
-      <c r="A14" s="21" t="s">
+      <c r="A14" t="s">
         <v>134</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" t="s">
         <v>135</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="21" t="s">
+      <c r="D14" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="21" t="s">
+      <c r="E14" t="s">
         <v>136</v>
       </c>
-      <c r="F14" s="21" t="s">
+      <c r="F14" t="s">
         <v>18</v>
       </c>
       <c r="G14" s="18">
         <v>46318</v>
       </c>
-      <c r="H14" s="21" t="s">
+      <c r="H14" t="s">
         <v>11</v>
       </c>
-      <c r="I14" s="21" t="s">
+      <c r="I14" t="s">
         <v>110</v>
       </c>
-      <c r="J14" s="21" t="s">
+      <c r="J14" t="s">
         <v>10</v>
       </c>
-      <c r="K14" s="21" t="s">
+      <c r="K14" t="s">
         <v>19</v>
       </c>
       <c r="L14">
         <v>200</v>
       </c>
-      <c r="M14" s="21" t="s">
+      <c r="M14" t="s">
         <v>53</v>
       </c>
-      <c r="N14" s="21" t="s">
+      <c r="N14" t="s">
         <v>60</v>
       </c>
       <c r="O14" s="18">
@@ -3362,13 +3365,13 @@
       <c r="Q14">
         <v>0</v>
       </c>
-      <c r="R14" s="21" t="s">
+      <c r="R14" t="s">
         <v>53</v>
       </c>
-      <c r="S14" s="21" t="s">
+      <c r="S14" t="s">
         <v>137</v>
       </c>
-      <c r="T14" s="21" t="s">
+      <c r="T14" t="s">
         <v>124</v>
       </c>
     </row>
@@ -3403,7 +3406,7 @@
     <col min="17" max="17" width="12" customWidth="1"/>
     <col min="18" max="18" width="10" customWidth="1"/>
     <col min="19" max="19" width="28" customWidth="1"/>
-    <col min="20" max="20" width="16.296875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="20.09765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="27.6">
@@ -3518,7 +3521,7 @@
       <c r="P2" s="5"/>
       <c r="Q2" s="4">
         <f ca="1">IF(P2&lt;&gt;"",P2-G2,TODAY()-G2)</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="R2" s="4" t="str">
         <f ca="1">IF(AND(O2&lt;&gt;"",O2&lt;TODAY(),K2&lt;&gt;"Completed",K2&lt;&gt;"Closed"),"Yes","No")</f>
@@ -3582,7 +3585,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="4">
         <f t="shared" ref="Q3:Q11" ca="1" si="1">IF(P3&lt;&gt;"",P3-G3,TODAY()-G3)</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="R3" s="4" t="str">
         <f t="shared" ref="R3:R11" ca="1" si="2">IF(AND(O3&lt;&gt;"",O3&lt;TODAY(),K3&lt;&gt;"Completed",K3&lt;&gt;"Closed"),"Yes","No")</f>
@@ -3646,7 +3649,7 @@
       <c r="P4" s="5"/>
       <c r="Q4" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R4" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3776,7 +3779,7 @@
       <c r="P6" s="5"/>
       <c r="Q6" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="R6" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3840,7 +3843,7 @@
       <c r="P7" s="5"/>
       <c r="Q7" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R7" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3904,7 +3907,7 @@
       <c r="P8" s="5"/>
       <c r="Q8" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="R8" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3968,7 +3971,7 @@
       <c r="P9" s="5"/>
       <c r="Q9" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="R9" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4032,7 +4035,7 @@
       <c r="P10" s="5"/>
       <c r="Q10" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="R10" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4162,7 +4165,7 @@
       <c r="P12" s="5"/>
       <c r="Q12" s="4">
         <f ca="1">IF(P12&lt;&gt;"",P12-G12,TODAY()-G12)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R12" s="4" t="str">
         <f ca="1">IF(AND(O12&lt;&gt;"",O12&lt;TODAY(),K12&lt;&gt;"Completed",K12&lt;&gt;"Closed"),"Yes","No")</f>
@@ -4226,7 +4229,7 @@
       <c r="P13" s="5"/>
       <c r="Q13" s="4">
         <f ca="1">IF(P13&lt;&gt;"",P13-G13,TODAY()-G13)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R13" s="4" t="str">
         <f ca="1">IF(AND(O13&lt;&gt;"",O13&lt;TODAY(),K13&lt;&gt;"Completed",K13&lt;&gt;"Closed"),"Yes","No")</f>
@@ -4290,7 +4293,7 @@
       <c r="P14" s="5"/>
       <c r="Q14" s="4">
         <f ca="1">IF(P14&lt;&gt;"",P14-G14,TODAY()-G14)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R14" s="4" t="str">
         <f ca="1">IF(AND(O14&lt;&gt;"",O14&lt;TODAY(),K14&lt;&gt;"Completed",K14&lt;&gt;"Closed"),"Yes","No")</f>
@@ -8212,20 +8215,20 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F200">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>F2="High"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K200">
-    <cfRule type="expression" dxfId="20" priority="3">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>K2="Closed"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="4">
+    <cfRule type="expression" dxfId="1" priority="4">
       <formula>K2="Completed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R200">
-    <cfRule type="expression" dxfId="18" priority="2">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>R2="Yes"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8294,7 +8297,7 @@
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="10.5" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="4" max="4" width="22.3984375" customWidth="1"/>
     <col min="5" max="5" width="6.796875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8386,7 +8389,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="B8">
         <f>COUNTIFS('Work Orders'!M2:M200,"Yes",'Work Orders'!N2:N200,"Pending")</f>
@@ -8422,7 +8425,7 @@
       </c>
       <c r="B11" s="14">
         <f ca="1">TODAY()</f>
-        <v>46318</v>
+        <v>46320</v>
       </c>
     </row>
     <row r="13" spans="1:5">
